--- a/Figure_Plot/figure_1/settings_sequence.xlsx
+++ b/Figure_Plot/figure_1/settings_sequence.xlsx
@@ -3,16 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-25710" yWindow="-3010" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="positive price case" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="negative price case" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -476,9 +475,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="24.375" customWidth="1" style="3" min="1" max="1"/>
+    <col width="24.33203125" customWidth="1" style="3" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1064,8 +1063,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <dimension ref="A1:Z7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <cols>
+    <col width="22.08203125" customWidth="1" style="3" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1146,478 +1148,496 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" customFormat="1" s="4">
+    <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
           <t>max-rate charge</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>-41.024</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U2" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W2" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X2" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y2" s="4" t="n">
-        <v>-35.2845</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="4">
+      <c r="B2" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>charge-for-charge</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W3" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X3" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>-35.2845</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="4">
+      <c r="B3" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W3" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X3" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>charge-for-discharge</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>-40.6599</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>-35.2845</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="4">
+      <c r="B4" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X4" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>discharge-for-charge</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>-40.5997</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X5" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>-35.2845</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" s="4">
+      <c r="B5" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="R5" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="S5" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="T5" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="U5" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="V5" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="W5" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="X5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
           <t>discharge-for-discharge</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>-37.2895</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X6" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y6" s="4" t="n">
-        <v>-35.2845</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="4">
+      <c r="B6" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
           <t>max-rate discharge</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>-37.218</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-40.7783</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-39.7194</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-36.242</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>-38.5318</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-33.9149</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-37.8115</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>-34.6703</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>-36.5286</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>-34.8896</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>-36.3381</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-37.6521</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>-38.6133</v>
-      </c>
-      <c r="O7" s="4" t="n">
-        <v>-37.268</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>-33.7451</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>-35.1532</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>-36.5669</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>-37.8556</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>-40.765</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>-41.3136</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>-39.0682</v>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>-38.0723</v>
-      </c>
-      <c r="X7" s="4" t="n">
-        <v>-34.7066</v>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>-35.2845</v>
+      <c r="B7" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W7" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X7" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1631,10 +1651,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="22.125" customWidth="1" style="3" min="1" max="1"/>
+    <col width="19.08203125" customWidth="1" style="3" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1723,43 +1743,43 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>14</v>
+        <v>-5</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L2" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M2" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N2" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O2" s="0" t="n">
         <v>5</v>
@@ -1768,34 +1788,31 @@
         <v>0</v>
       </c>
       <c r="Q2" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R2" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S2" s="0" t="n">
         <v>5</v>
       </c>
       <c r="T2" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U2" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="V2" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="W2" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X2" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y2" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="Z2" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1805,43 +1822,43 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>22</v>
-      </c>
       <c r="L3" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M3" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N3" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O3" s="0" t="n">
         <v>5</v>
@@ -1850,34 +1867,31 @@
         <v>0</v>
       </c>
       <c r="Q3" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R3" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S3" s="0" t="n">
         <v>5</v>
       </c>
       <c r="T3" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U3" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="V3" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="W3" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X3" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y3" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="Z3" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1887,43 +1901,43 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>5</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M4" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O4" s="0" t="n">
         <v>5</v>
@@ -1932,34 +1946,31 @@
         <v>0</v>
       </c>
       <c r="Q4" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R4" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S4" s="0" t="n">
         <v>5</v>
       </c>
       <c r="T4" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U4" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="V4" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="W4" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X4" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y4" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="Z4" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1969,25 +1980,25 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>5</v>
@@ -1996,51 +2007,48 @@
         <v>0</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="M5" s="0" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N5" s="0" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>12</v>
+        <v>-5</v>
       </c>
       <c r="P5" s="0" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="Q5" s="0" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="R5" s="0" t="n">
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="S5" s="0" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="T5" s="0" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="U5" s="0" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="V5" s="0" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W5" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="Y5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2051,10 +2059,10 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
@@ -2063,31 +2071,31 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M6" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N6" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O6" s="0" t="n">
         <v>5</v>
@@ -2096,34 +2104,31 @@
         <v>0</v>
       </c>
       <c r="Q6" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="R6" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S6" s="0" t="n">
         <v>5</v>
       </c>
       <c r="T6" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U6" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="V6" s="0" t="n">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="W6" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="X6" s="0" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="0" t="n">
         <v>5</v>
-      </c>
-      <c r="Z6" s="0" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2133,10 +2138,10 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>4</v>
@@ -2145,586 +2150,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="J7" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="V7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="W7" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="X7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z7" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
-  <cols>
-    <col width="19.125" customWidth="1" style="3" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E1" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="G1" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="H1" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="I1" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="J1" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="K1" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="L1" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="M1" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="N1" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="O1" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="P1" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="R1" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="S1" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="T1" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="U1" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="V1" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="W1" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="X1" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="0" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>max-rate charge</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U2" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V2" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="W2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="X2" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>charge-for-charge</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U3" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V3" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="W3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="X3" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>charge-for-discharge</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>-0.9999999999999982</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H4" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="I4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J4" s="0" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U4" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V4" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="W4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="X4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y4" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>discharge-for-charge</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="Q5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="S5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="V5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="X5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>discharge-for-discharge</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J6" s="0" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="V6" s="0" t="n">
-        <v>-4.999999999999998</v>
-      </c>
-      <c r="W6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y6" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>max-rate discharge</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>-4.999999999999998</v>
+        <v>-5</v>
       </c>
       <c r="I7" s="0" t="n">
         <v>-5</v>
@@ -2766,7 +2198,7 @@
         <v>-5</v>
       </c>
       <c r="V7" s="0" t="n">
-        <v>-4.999999999999998</v>
+        <v>-5</v>
       </c>
       <c r="W7" s="0" t="n">
         <v>5</v>
